--- a/Driving_Experience_Teilnehmer.xlsx
+++ b/Driving_Experience_Teilnehmer.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Swayam/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CA201C-9DEA-E24A-AB58-C388EB5A1DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Fahrerlebnis_Teilnehmer" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Fahrerlebnis_Teilnehmer" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -24,65 +28,62 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t xml:space="preserve">Fahrerlebnis – Teilnehmerliste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please read before filling in the data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Tragen Sie eine Zeile pro teilnehmender Person ein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  'Fahrerlebnis' nur ueber das Dropdown waehlen: selbstfahren oder beifahrer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  'C_Klasse_Fuehrerschein' nur ueber das Dropdown waehlen: Ja oder Nein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Wenn 'Fahrerlebnis' = selbstfahren, MUSS 'C_Klasse_Fuehrerschein' = Ja sein.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Die Gesamtzahl der Zeilen muss mit der im Tally-Formular angegebenen Personenzahl uebereinstimmen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Speichern Sie die Datei im .xlsx-Format und laden Sie sie im Tally-Formular hoch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fahrerlebnis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_Klasse_Fuehrerschein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selbstfahren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;- Beispiel, bitte loeschen</t>
+    <t>Fahrerlebnis – Teilnehmerliste</t>
+  </si>
+  <si>
+    <t>Please read before filling in the data.</t>
+  </si>
+  <si>
+    <t>•  Tragen Sie eine Zeile pro teilnehmender Person ein.</t>
+  </si>
+  <si>
+    <t>•  'Fahrerlebnis' nur ueber das Dropdown waehlen: selbstfahren oder beifahrer.</t>
+  </si>
+  <si>
+    <t>•  'C_Klasse_Fuehrerschein' nur ueber das Dropdown waehlen: Ja oder Nein.</t>
+  </si>
+  <si>
+    <t>•  Wenn 'Fahrerlebnis' = selbstfahren, MUSS 'C_Klasse_Fuehrerschein' = Ja sein.</t>
+  </si>
+  <si>
+    <t>•  Die Gesamtzahl der Zeilen muss mit der im Tally-Formular angegebenen Personenzahl uebereinstimmen.</t>
+  </si>
+  <si>
+    <t>•  Speichern Sie die Datei im .xlsx-Format und laden Sie sie im Tally-Formular hoch.</t>
+  </si>
+  <si>
+    <t>Vorname</t>
+  </si>
+  <si>
+    <t>Nachname</t>
+  </si>
+  <si>
+    <t>C_Klasse_Fuehrerschein</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Schmidt</t>
+  </si>
+  <si>
+    <t>selbstfahren</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>&lt;- Beispiel, bitte loeschen</t>
+  </si>
+  <si>
+    <t>Fahr-Art</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,56 +92,36 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -164,14 +145,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -187,73 +168,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -312,47 +246,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -360,12 +310,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -394,7 +344,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -415,7 +365,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -466,7 +416,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -484,109 +434,82 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -594,366 +517,366 @@
         <v>9</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -961,21 +884,16 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Bitte 'selbstfahren' oder 'beifahrer' waehlen." errorStyle="stop" errorTitle="Ungueltiger Wert" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C60" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Ungueltiger Wert" error="Bitte 'selbstfahren' oder 'beifahrer' waehlen." sqref="C2:C60" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"selbstfahren,beifahrer"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Bitte 'Ja' oder 'Nein' waehlen." errorStyle="stop" errorTitle="Ungueltiger Wert" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D60" type="list">
+    <dataValidation type="list" allowBlank="1" errorTitle="Ungueltiger Wert" error="Bitte 'Ja' oder 'Nein' waehlen." sqref="D2:D60" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>